--- a/Data/Rehires/Workday_Rehire_Poland_Regression_PK14.xlsx
+++ b/Data/Rehires/Workday_Rehire_Poland_Regression_PK14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD46B6E-A355-4ABA-A118-A3A2D3C1EAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62406167-9B75-49C8-A393-12635D3E497F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -54,9 +54,6 @@
     <t>SupervisoryOrganisation</t>
   </si>
   <si>
-    <t>ExistingPreHire</t>
-  </si>
-  <si>
     <t>HireDate</t>
   </si>
   <si>
@@ -132,48 +129,51 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>Assign Paygroup</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>10698988</t>
+  </si>
+  <si>
+    <t>PolandOne</t>
+  </si>
+  <si>
+    <t>TwentyFiveJulyTwentiEight</t>
+  </si>
+  <si>
+    <t>765 Store Management (Jizur Buzese (10226524))</t>
+  </si>
+  <si>
+    <t>ReHire</t>
+  </si>
+  <si>
+    <t>Auto 8859497</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>RE024_NEW</t>
+  </si>
+  <si>
+    <t>5 Days</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>10698560</t>
-  </si>
-  <si>
-    <t>PolandOne</t>
-  </si>
-  <si>
-    <t>TwentyFiveJuneSixteen</t>
-  </si>
-  <si>
-    <t>765 Store Management (Jizur Buzese (10226524))</t>
-  </si>
-  <si>
-    <t>ReHire</t>
-  </si>
-  <si>
-    <t>Auto 45697559</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>RE024_NEW</t>
-  </si>
-  <si>
-    <t>5 Days (Poland)</t>
-  </si>
-  <si>
     <t>Automation Comments here….</t>
   </si>
   <si>
@@ -204,7 +204,7 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698561</t>
+    <t>10698989</t>
   </si>
   <si>
     <t>PolandTwo</t>
@@ -231,10 +231,13 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>PolandSix</t>
-  </si>
-  <si>
-    <t>Auto 32755888</t>
+    <t>10699002</t>
+  </si>
+  <si>
+    <t>PolandEleven</t>
+  </si>
+  <si>
+    <t>Auto 33517823</t>
   </si>
   <si>
     <t>Department Manager_NEW</t>
@@ -243,22 +246,19 @@
     <t>Test4</t>
   </si>
   <si>
+    <t>10698992</t>
+  </si>
+  <si>
     <t>PolandFive</t>
   </si>
   <si>
     <t>Test5</t>
   </si>
   <si>
-    <t>10698571</t>
+    <t>10699005</t>
   </si>
   <si>
     <t>PolandFourteen</t>
-  </si>
-  <si>
-    <t>10698564</t>
-  </si>
-  <si>
-    <t>10698563</t>
   </si>
 </sst>
 </file>
@@ -277,11 +277,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
@@ -314,7 +314,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,13 +329,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -345,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -383,15 +377,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -404,14 +414,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -431,7 +438,7 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -458,12 +465,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BO18"/>
   <sheetFormatPr defaultRowHeight="15.6" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
@@ -753,202 +754,197 @@
     <col min="4" max="4" width="7.5546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="48.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="36.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="9.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="18.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="26.44140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="16.77734375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="17" style="1" customWidth="1"/>
-    <col min="24" max="24" width="29.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="20.88671875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="2" customWidth="1"/>
-    <col min="27" max="27" width="16" style="1" customWidth="1"/>
-    <col min="28" max="28" width="18.5546875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="18.21875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="6" style="1" customWidth="1"/>
-    <col min="31" max="31" width="12.77734375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="15.109375" style="1" customWidth="1"/>
-    <col min="33" max="33" width="9" style="1" customWidth="1"/>
-    <col min="34" max="34" width="16.77734375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="21" style="1" customWidth="1"/>
-    <col min="36" max="36" width="17" style="1" customWidth="1"/>
-    <col min="37" max="37" width="21" style="1" customWidth="1"/>
-    <col min="38" max="38" width="17.5546875" customWidth="1"/>
-    <col min="39" max="40" width="22.44140625" style="1" customWidth="1"/>
-    <col min="41" max="41" width="18.21875" style="1" customWidth="1"/>
-    <col min="42" max="42" width="17.77734375" style="1" customWidth="1"/>
-    <col min="43" max="43" width="5.88671875" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.109375" style="1" customWidth="1"/>
-    <col min="45" max="45" width="7" style="1" customWidth="1"/>
-    <col min="46" max="46" width="10.77734375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="13.5546875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="20.21875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="9.88671875" style="1" customWidth="1"/>
-    <col min="50" max="50" width="11.88671875" style="1" customWidth="1"/>
-    <col min="51" max="51" width="15.88671875" style="1" customWidth="1"/>
-    <col min="52" max="52" width="15" style="1" customWidth="1"/>
-    <col min="53" max="53" width="16.33203125" style="2" customWidth="1"/>
-    <col min="54" max="54" width="53.6640625" style="2" customWidth="1"/>
-    <col min="55" max="55" width="23.77734375" style="2" customWidth="1"/>
-    <col min="56" max="56" width="9" style="1" customWidth="1"/>
-    <col min="57" max="57" width="30.109375" style="1" customWidth="1"/>
-    <col min="58" max="58" width="20.33203125" style="1" customWidth="1"/>
-    <col min="59" max="59" width="14.44140625" style="1" customWidth="1"/>
-    <col min="60" max="60" width="17.109375" style="1" customWidth="1"/>
-    <col min="61" max="61" width="11.5546875" style="1" customWidth="1"/>
-    <col min="62" max="62" width="15.44140625" style="1" customWidth="1"/>
-    <col min="63" max="64" width="11.109375" style="1" customWidth="1"/>
-    <col min="65" max="65" width="16.6640625" style="1" customWidth="1"/>
-    <col min="66" max="66" width="18.109375" style="1" customWidth="1"/>
-    <col min="67" max="67" width="17.109375" style="1" customWidth="1"/>
-    <col min="68" max="68" width="16.5546875" style="1" customWidth="1"/>
-    <col min="69" max="69" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="31.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.21875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="26.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="16.77734375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17" style="1" customWidth="1"/>
+    <col min="23" max="23" width="29.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="20.88671875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16" style="3" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" customWidth="1"/>
+    <col min="27" max="27" width="18.5546875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="18.21875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="6" style="1" customWidth="1"/>
+    <col min="30" max="30" width="12.77734375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.109375" style="1" customWidth="1"/>
+    <col min="32" max="32" width="9" style="1" customWidth="1"/>
+    <col min="33" max="33" width="16.77734375" style="1" customWidth="1"/>
+    <col min="34" max="34" width="21" style="1" customWidth="1"/>
+    <col min="35" max="35" width="17" style="1" customWidth="1"/>
+    <col min="36" max="36" width="21" style="1" customWidth="1"/>
+    <col min="37" max="37" width="17.5546875" customWidth="1"/>
+    <col min="38" max="39" width="22.44140625" style="1" customWidth="1"/>
+    <col min="40" max="40" width="18.21875" style="1" customWidth="1"/>
+    <col min="41" max="41" width="17.77734375" style="1" customWidth="1"/>
+    <col min="42" max="42" width="5.88671875" style="1" customWidth="1"/>
+    <col min="43" max="43" width="15.109375" style="1" customWidth="1"/>
+    <col min="44" max="44" width="7" style="1" customWidth="1"/>
+    <col min="45" max="45" width="10.77734375" style="1" customWidth="1"/>
+    <col min="46" max="46" width="13.5546875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="20.21875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="9.88671875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="11.88671875" style="1" customWidth="1"/>
+    <col min="50" max="50" width="15.88671875" style="1" customWidth="1"/>
+    <col min="51" max="51" width="15" style="1" customWidth="1"/>
+    <col min="52" max="52" width="16.33203125" style="3" customWidth="1"/>
+    <col min="53" max="53" width="53.6640625" style="3" customWidth="1"/>
+    <col min="54" max="54" width="23.77734375" style="3" customWidth="1"/>
+    <col min="55" max="55" width="9" style="1" customWidth="1"/>
+    <col min="56" max="56" width="30.109375" style="1" customWidth="1"/>
+    <col min="57" max="57" width="20.33203125" style="1" customWidth="1"/>
+    <col min="58" max="58" width="14.44140625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="17.109375" style="1" customWidth="1"/>
+    <col min="60" max="60" width="11.5546875" style="1" customWidth="1"/>
+    <col min="61" max="61" width="15.44140625" style="1" customWidth="1"/>
+    <col min="62" max="63" width="11.109375" style="1" customWidth="1"/>
+    <col min="64" max="64" width="16.6640625" style="1" customWidth="1"/>
+    <col min="65" max="65" width="18.109375" style="1" customWidth="1"/>
+    <col min="66" max="66" width="17.109375" style="1" customWidth="1"/>
+    <col min="67" max="67" width="16.5546875" style="1" customWidth="1"/>
+    <col min="68" max="68" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="1" customFormat="1" ht="14.55" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:32" s="1" customFormat="1" ht="14.55" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="8">
+        <f ca="1">TODAY()-1</f>
+        <v>45869</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="I2" s="8" t="str">
-        <f>F2&amp;" "&amp;G2</f>
-        <v>PolandOne TwentyFiveJuneSixteen</v>
-      </c>
-      <c r="J2" s="9">
-        <f ca="1">TODAY()-1</f>
-        <v>45826</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>41</v>
@@ -962,501 +958,506 @@
       <c r="N2" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="14">
+        <v>765</v>
+      </c>
+      <c r="P2" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="15">
-        <v>765</v>
-      </c>
-      <c r="Q2" s="16">
-        <v>40</v>
-      </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="10" t="s">
+      <c r="S2" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="U2" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="W2" t="s">
+      <c r="V2" t="s">
         <v>50</v>
       </c>
-      <c r="X2" s="19" t="s">
+      <c r="W2" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="X2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Z2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="9">
-        <f ca="1">J2</f>
-        <v>45826</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC2" s="11" t="s">
+      <c r="Y2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" s="8">
+        <f ca="1">I2</f>
+        <v>45869</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AD2" s="20" t="s">
+      <c r="AC2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AD2" s="10" t="s">
         <v>55</v>
       </c>
+      <c r="AE2" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="AF2" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG2" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="8" t="str">
-        <f t="shared" ref="I3:I6" si="0">F3&amp;" "&amp;G3</f>
-        <v>PolandTwo TwentyFiveJuneSixteen</v>
-      </c>
-      <c r="J3" s="9">
+      <c r="I3" s="8">
         <f ca="1">TODAY()-1</f>
-        <v>45826</v>
+        <v>45869</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="O3" s="12" t="s">
-        <v>45</v>
+      <c r="N3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="22">
+        <v>765</v>
       </c>
       <c r="P3" s="23">
-        <v>765</v>
-      </c>
-      <c r="Q3" s="24">
         <v>40</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="Q3" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="S3" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" s="10" t="s">
+      <c r="R3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="18" t="s">
+      <c r="U3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="W3" t="s">
+      <c r="V3" t="s">
         <v>65</v>
       </c>
-      <c r="X3" s="19" t="s">
+      <c r="W3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" s="19" t="s">
+      <c r="X3" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Z3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA3" s="9">
-        <f ca="1">J3</f>
-        <v>45826</v>
-      </c>
-      <c r="AB3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC3" s="11" t="s">
+      <c r="Y3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" s="8">
+        <f ca="1">I3</f>
+        <v>45869</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AD3" s="20" t="s">
+      <c r="AC3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AE3" s="11" t="s">
+      <c r="AD3" s="10" t="s">
         <v>55</v>
       </c>
+      <c r="AE3" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="AF3" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG3" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="8">
+        <f ca="1">TODAY()-1</f>
+        <v>45869</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="22">
+        <v>765</v>
+      </c>
+      <c r="P4" s="23">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" s="8">
+        <f ca="1">I4</f>
+        <v>45869</v>
+      </c>
+      <c r="AA4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC4" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF4" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="8">
+        <f ca="1">TODAY()-1</f>
+        <v>45869</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="22">
+        <v>765</v>
+      </c>
+      <c r="P5" s="23">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="X5" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" s="8">
+        <f ca="1">I5</f>
+        <v>45869</v>
+      </c>
+      <c r="AA5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC5" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD5" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE5" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF5" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="8">
+        <f ca="1">TODAY()-1</f>
+        <v>45869</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>PolandSix TwentyFiveJuneSixteen</v>
-      </c>
-      <c r="J4" s="9">
-        <f ca="1">TODAY()-1</f>
-        <v>45826</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="23">
+      <c r="K6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="22">
         <v>765</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="P6" s="23">
         <v>40</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="Q6" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="S4" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U4" s="10" t="s">
+      <c r="R6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="V4" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X4" s="19" t="s">
+      <c r="U6" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="V6" t="s">
+        <v>65</v>
+      </c>
+      <c r="W6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" s="19" t="s">
+      <c r="X6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Z4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA4" s="9">
-        <f ca="1">J4</f>
-        <v>45826</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC4" s="11" t="s">
+      <c r="Y6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" s="8">
+        <f ca="1">I6</f>
+        <v>45869</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB6" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AD4" s="20" t="s">
+      <c r="AC6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AE4" s="11" t="s">
+      <c r="AD6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="AF4" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG4" s="22" t="s">
+      <c r="AE6" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF6" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>PolandFive TwentyFiveJuneSixteen</v>
-      </c>
-      <c r="J5" s="9">
-        <f ca="1">TODAY()-1</f>
-        <v>45826</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="23">
-        <v>765</v>
-      </c>
-      <c r="Q5" s="24">
-        <v>40</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="S5" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="W5" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y5" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA5" s="9">
-        <f ca="1">J5</f>
-        <v>45826</v>
-      </c>
-      <c r="AB5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD5" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF5" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG5" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>PolandFourteen TwentyFiveJuneSixteen</v>
-      </c>
-      <c r="J6" s="9">
-        <f ca="1">TODAY()-1</f>
-        <v>45826</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="23">
-        <v>765</v>
-      </c>
-      <c r="Q6" s="24">
-        <v>40</v>
-      </c>
-      <c r="R6" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="S6" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="T6" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="W6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X6" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA6" s="9">
-        <f ca="1">J6</f>
-        <v>45826</v>
-      </c>
-      <c r="AB6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC6" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD6" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF6" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG6" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:33" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:32" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="7:7" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="7:7" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD6 K2:K6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC6 J2:J6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>
